--- a/output/xgb_reg/03_model_tuning/tuning_log.xlsx
+++ b/output/xgb_reg/03_model_tuning/tuning_log.xlsx
@@ -507,19 +507,19 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>2.949261</v>
+        <v>2.947863</v>
       </c>
       <c r="D3" t="b">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3689</v>
+        <v>2.3516</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0789</v>
+        <v>2.0685</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3973</v>
+        <v>2.3923</v>
       </c>
     </row>
     <row r="4">
@@ -557,19 +557,19 @@
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>2.949261</v>
+        <v>2.955423</v>
       </c>
       <c r="D5" t="b">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3689</v>
+        <v>2.338</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0789</v>
+        <v>2.0848</v>
       </c>
       <c r="G5" t="n">
-        <v>2.3973</v>
+        <v>2.3976</v>
       </c>
     </row>
     <row r="6">
@@ -582,19 +582,19 @@
         <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>2.949954</v>
+        <v>2.961491</v>
       </c>
       <c r="D6" t="b">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>2.3646</v>
+        <v>2.3185</v>
       </c>
       <c r="F6" t="n">
-        <v>2.0786</v>
+        <v>2.0703</v>
       </c>
       <c r="G6" t="n">
-        <v>2.3971</v>
+        <v>2.3972</v>
       </c>
     </row>
     <row r="7">
@@ -607,19 +607,19 @@
         <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>2.952621</v>
+        <v>2.96697</v>
       </c>
       <c r="D7" t="b">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>2.3564</v>
+        <v>2.3005</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0851</v>
+        <v>2.0527</v>
       </c>
       <c r="G7" t="n">
-        <v>2.3986</v>
+        <v>2.396</v>
       </c>
     </row>
     <row r="8">
@@ -632,19 +632,19 @@
         <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>2.956163</v>
+        <v>2.972003</v>
       </c>
       <c r="D8" t="b">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>2.3494</v>
+        <v>2.3142</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0785</v>
+        <v>2.0763</v>
       </c>
       <c r="G8" t="n">
-        <v>2.3993</v>
+        <v>2.4049</v>
       </c>
     </row>
     <row r="9">
@@ -657,19 +657,19 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>2.966478</v>
+        <v>2.950872</v>
       </c>
       <c r="D9" t="b">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>2.3251</v>
+        <v>2.3581</v>
       </c>
       <c r="F9" t="n">
-        <v>2.0732</v>
+        <v>2.0763</v>
       </c>
       <c r="G9" t="n">
-        <v>2.4023</v>
+        <v>2.3965</v>
       </c>
     </row>
     <row r="10">
@@ -682,19 +682,19 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>2.950266</v>
+        <v>2.949261</v>
       </c>
       <c r="D10" t="b">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>2.3604</v>
+        <v>2.3689</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0756</v>
+        <v>2.0789</v>
       </c>
       <c r="G10" t="n">
-        <v>2.3963</v>
+        <v>2.3973</v>
       </c>
     </row>
     <row r="11">
@@ -707,44 +707,44 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>3.015836</v>
+        <v>2.983986</v>
       </c>
       <c r="D11" t="b">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>2.205</v>
+        <v>2.2167</v>
       </c>
       <c r="F11" t="n">
-        <v>2.0561</v>
+        <v>2.0957</v>
       </c>
       <c r="G11" t="n">
-        <v>2.4156</v>
+        <v>2.3993</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>第2轮</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>第2轮</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="C12" t="n">
-        <v>3.028929</v>
-      </c>
-      <c r="D12" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>2.1561</v>
-      </c>
-      <c r="F12" t="n">
-        <v>2.082</v>
-      </c>
-      <c r="G12" t="n">
-        <v>2.4193</v>
+      <c r="C12" s="2" t="n">
+        <v>2.946402</v>
+      </c>
+      <c r="D12" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>2.3679</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>2.0779</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>2.3949</v>
       </c>
     </row>
     <row r="13">
@@ -757,19 +757,19 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>2.981975</v>
+        <v>2.972746</v>
       </c>
       <c r="D13" t="b">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3</v>
+        <v>2.3251</v>
       </c>
       <c r="F13" t="n">
-        <v>2.0458</v>
+        <v>2.0529</v>
       </c>
       <c r="G13" t="n">
-        <v>2.4061</v>
+        <v>2.4044</v>
       </c>
     </row>
     <row r="14">
@@ -782,19 +782,19 @@
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>2.999043</v>
+        <v>2.956463</v>
       </c>
       <c r="D14" t="b">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1977</v>
+        <v>2.3345</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0895</v>
+        <v>2.0697</v>
       </c>
       <c r="G14" t="n">
-        <v>2.4062</v>
+        <v>2.396</v>
       </c>
     </row>
     <row r="15">
@@ -807,19 +807,19 @@
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>2.949261</v>
+        <v>2.968129</v>
       </c>
       <c r="D15" t="b">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3689</v>
+        <v>2.2765</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0789</v>
+        <v>2.0742</v>
       </c>
       <c r="G15" t="n">
-        <v>2.3973</v>
+        <v>2.3955</v>
       </c>
     </row>
     <row r="16">
@@ -832,19 +832,19 @@
         <v>14</v>
       </c>
       <c r="C16" t="n">
-        <v>2.949261</v>
+        <v>2.970954</v>
       </c>
       <c r="D16" t="b">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3689</v>
+        <v>2.2616</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0789</v>
+        <v>2.079</v>
       </c>
       <c r="G16" t="n">
-        <v>2.3973</v>
+        <v>2.3956</v>
       </c>
     </row>
     <row r="17">
@@ -857,19 +857,19 @@
         <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>2.949898</v>
+        <v>2.959323</v>
       </c>
       <c r="D17" t="b">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3558</v>
+        <v>2.3356</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0774</v>
+        <v>2.0764</v>
       </c>
       <c r="G17" t="n">
-        <v>2.3955</v>
+        <v>2.3991</v>
       </c>
     </row>
     <row r="18">
@@ -882,19 +882,19 @@
         <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>2.949261</v>
+        <v>2.952889</v>
       </c>
       <c r="D18" t="b">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>2.3689</v>
+        <v>2.3451</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0789</v>
+        <v>2.0884</v>
       </c>
       <c r="G18" t="n">
-        <v>2.3973</v>
+        <v>2.3974</v>
       </c>
     </row>
     <row r="19">
@@ -907,19 +907,19 @@
         <v>17</v>
       </c>
       <c r="C19" t="n">
-        <v>2.952659</v>
+        <v>2.980126</v>
       </c>
       <c r="D19" t="b">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>2.3505</v>
+        <v>2.2793</v>
       </c>
       <c r="F19" t="n">
-        <v>2.0691</v>
+        <v>2.0598</v>
       </c>
       <c r="G19" t="n">
-        <v>2.3957</v>
+        <v>2.403</v>
       </c>
     </row>
     <row r="20">
@@ -932,19 +932,19 @@
         <v>18</v>
       </c>
       <c r="C20" t="n">
-        <v>2.952749</v>
+        <v>2.996093</v>
       </c>
       <c r="D20" t="b">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>2.3232</v>
+        <v>2.2363</v>
       </c>
       <c r="F20" t="n">
-        <v>2.0916</v>
+        <v>2.0822</v>
       </c>
       <c r="G20" t="n">
-        <v>2.3941</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="21">
@@ -957,44 +957,44 @@
         <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>2.984266</v>
+        <v>2.949261</v>
       </c>
       <c r="D21" t="b">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>2.2526</v>
+        <v>2.3689</v>
       </c>
       <c r="F21" t="n">
-        <v>2.0669</v>
+        <v>2.0789</v>
       </c>
       <c r="G21" t="n">
-        <v>2.4023</v>
+        <v>2.3973</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>第2轮</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>第2轮</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
         <v>20</v>
       </c>
-      <c r="C22" s="2" t="n">
-        <v>2.944861</v>
-      </c>
-      <c r="D22" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>2.3675</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>2.0777</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>2.3937</v>
+      <c r="C22" t="n">
+        <v>2.992665</v>
+      </c>
+      <c r="D22" t="b">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2.2877</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.0416</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.4113</v>
       </c>
     </row>
   </sheetData>
